--- a/data/02_Daily_Sheets/Expressions_2026-05-31.xlsx
+++ b/data/02_Daily_Sheets/Expressions_2026-05-31.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CHI-20260531-001</t>
+          <t>CHI-20260531-010</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,39 +481,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>失联</t>
+          <t>签订合同</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Separable Verb</t>
+          <t>Verb-Noun phrase</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>shīlián</t>
+          <t>qiāndìng hétong</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>연락이 끊기다, 실종되다.</t>
+          <t>계약을 체결하다</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>...拒绝支付任何赔偿，甚至失联跑路。</t>
+          <t>...用人单位未签订劳动合同、未缴纳工伤保险...</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>他已经好几天没来上班了，电话也打不通，好像失联了。</t>
+          <t>我们公司今天和新客户签订了一份重要的合作合同。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CHI-20260531-002</t>
+          <t>CHI-20260531-011</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -528,39 +528,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>跑路</t>
+          <t>缴纳</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Colloquialism</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>pǎolù</t>
+          <t>jiǎonà</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>도망가다, (책임을 회피하고) 잠적하다.</t>
+          <t>납부하다 (세금, 비용 등을 내다)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>...拒绝支付任何赔偿，甚至失联跑路。</t>
+          <t>...用人单位未签订劳动合同、未缴纳工伤保险...</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>那家小公司老板欠了员工工资就跑路了，真是太不负责任了。</t>
+          <t>每个月公司都会按时为员工缴纳社会保险。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CHI-20260531-003</t>
+          <t>CHI-20260531-012</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>凭借</t>
+          <t>启动</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -585,304 +585,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>píngjiè</t>
+          <t>qǐdòng</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>~에 의지하여, ~을 바탕으로.</t>
+          <t>시작하다, 가동하다, 발동하다</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>肖战、马丽分别凭借电影《得闲谨制》与《水饺皇后》，...</t>
+          <t>贝德美正式启动“旧物新生自然有续”环保计划...</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>他凭借自己的努力和才华，终于在公司里获得了晋升。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CHI-20260531-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Scraped_News</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>融合</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Verb / Noun</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>rónghé</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>융합하다, 통합하다, 융합.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>当百年遗产“邂逅”文旅潮流 工商文旅融合解锁跨界“...</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>现代科技与传统文化如何更好地融合，是我们需要思考的问题。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CHI-20260531-005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Scraped_News</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>出炉</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Colloquialism</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>chū lú</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>(결과, 제품 등이) 나오다, 발표되다</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>高考成绩出炉</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>经过几个月的紧张筹备，我们公司的新产品终于出炉了。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CHI-20260531-006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Scraped_News</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>致敬</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Verb</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>zhì jìng</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>경의를 표하다, 존경을 표하다</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>致敬劳动者</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>在这个特殊的日子里，我们向所有医护人员致敬。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CHI-20260531-007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Scraped_News</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>聚焦</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Verb</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>jù jiāo</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>초점을 맞추다, 집중하다</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>聚焦赣江流域水生...</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>下周的会议将聚焦如何提高市场份额的问题，请大家提前做好准备。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CHI-20260531-008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Scraped_News</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>服役</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Separable Verb</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>fúyì</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>복무하다, 근무하다, (기계 등이) 운행되다</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>北京地铁一号线“服役”20多年的老列车在逐渐“告别...</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>这台服务器已经服役五年了，是时候考虑更新换代了。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CHI-20260531-009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Scraped_News</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>咨询</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Verb</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>zīxún</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>상담하다, 문의하다</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>我曾直接参与学校的心理健康咨询工作。</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>如果你对新政策有疑问，可以去人事部咨询。</t>
+          <t>公司下周将启动一个新的市场推广项目。</t>
         </is>
       </c>
     </row>
